--- a/Result/profitability/6426.xlsx
+++ b/Result/profitability/6426.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM54"/>
+  <dimension ref="A1:AM55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7288,6 +7288,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>6426</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>208</v>
+      </c>
+      <c r="D55" t="n">
+        <v>91</v>
+      </c>
+      <c r="E55" t="n">
+        <v>117</v>
+      </c>
+      <c r="F55" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>75</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>36.14%</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>6</v>
+      </c>
+      <c r="J55" t="n">
+        <v>81</v>
+      </c>
+      <c r="K55" t="n">
+        <v>86</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.03500000000000003</v>
+      </c>
+      <c r="N55" t="n">
+        <v>27.195</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.4242270653826661</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>-2.819672131147541</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.797411647585864</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK55" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
